--- a/bd_macro_data.xlsx
+++ b/bd_macro_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Downloads\DCM Macro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\DCM_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB938CFD-1BAA-4061-A4D1-C397456279D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB6633-3D2B-44B6-AE25-5DC672921F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1245,8 +1245,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{889AA22C-0816-4265-8341-00AFB962B62C}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/bd_macro_data.xlsx
+++ b/bd_macro_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\DCM_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB6633-3D2B-44B6-AE25-5DC672921F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2188AB7-9C58-434D-8390-46F6038140B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,8 +478,20 @@
     <t>June 29, 2026</t>
   </si>
   <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>New Monetary Policy declared. The contractionary stance prevails with a new rule to improve credit growth - limiting spread between the deposit and lending rates of commercial banks. The move has been highly crticized already and practitioners believe the central bank will move away from this action.</t>
+  </si>
+  <si>
+    <t>Md. Sohel Rahman</t>
+  </si>
+  <si>
+    <t>Industry Professionals Only - Domestic Bangladeshi Market</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">DCM Weekly : </t>
+      <t xml:space="preserve">The DCM Weekly : </t>
     </r>
     <r>
       <rPr>
@@ -500,18 +512,6 @@
       </rPr>
       <t xml:space="preserve"> Macro</t>
     </r>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>New Monetary Policy declared. The contractionary stance prevails with a new rule to improve credit growth - limiting spread between the deposit and lending rates of commercial banks. The move has been highly crticized already and practitioners believe the central bank will move away from this action.</t>
-  </si>
-  <si>
-    <t>Md. Sohel Rahman</t>
-  </si>
-  <si>
-    <t>Industry Professionals Only - Domestic Bangladeshi Market</t>
   </si>
 </sst>
 </file>
@@ -636,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -662,9 +662,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1208,8 +1205,8 @@
       <c r="A3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>150</v>
+      <c r="B3" s="7" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1225,7 +1222,7 @@
         <v>42</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1233,7 +1230,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="72" customHeight="1" x14ac:dyDescent="0.35">
@@ -1241,15 +1238,12 @@
         <v>44</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{889AA22C-0816-4265-8341-00AFB962B62C}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2714,8 +2708,8 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>151</v>
+      <c r="A15" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="B15" s="11">
         <v>122.75</v>

--- a/bd_macro_data.xlsx
+++ b/bd_macro_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\DCM_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2188AB7-9C58-434D-8390-46F6038140B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C64FF-E722-4B8B-93C5-1D52D4890284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="166">
   <si>
     <t>Bangladesh Macro Weekly  -  Data Input Workbook</t>
   </si>
@@ -154,9 +154,6 @@
     <t>Rates, FX, the External Sector &amp; Global Markets</t>
   </si>
   <si>
-    <t>PreparedBy</t>
-  </si>
-  <si>
     <t>ForAudience</t>
   </si>
   <si>
@@ -475,23 +472,14 @@
     <t>Optional spotlight slide for a policy change, circular, law or monetary-policy issue. Leave Title and ALL Points blank to hide the slide entirely. Add as many 'Point' rows as you need.</t>
   </si>
   <si>
-    <t>June 29, 2026</t>
-  </si>
-  <si>
     <t>2026-06-01</t>
   </si>
   <si>
-    <t>New Monetary Policy declared. The contractionary stance prevails with a new rule to improve credit growth - limiting spread between the deposit and lending rates of commercial banks. The move has been highly crticized already and practitioners believe the central bank will move away from this action.</t>
-  </si>
-  <si>
-    <t>Md. Sohel Rahman</t>
-  </si>
-  <si>
-    <t>Industry Professionals Only - Domestic Bangladeshi Market</t>
+    <t>July 04, 2026</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">The DCM Weekly : </t>
+      <t xml:space="preserve">DCM Weekly : </t>
     </r>
     <r>
       <rPr>
@@ -512,6 +500,51 @@
       </rPr>
       <t xml:space="preserve"> Macro</t>
     </r>
+  </si>
+  <si>
+    <t>M Sohel Rahman, DHAKA, BD</t>
+  </si>
+  <si>
+    <t>For Quick Reference Only - Domestic &amp; Global Markets</t>
+  </si>
+  <si>
+    <t>Bangladesh Bank maintains its contractionary policy rate at 10.0% through H1FY27 to anchor inflation—now easing to 9.4% from an 11.7% peak—while unveiling a Tk. 60,000 crore stimulus package aimed at reviving private credit, industrial output, and generating 25 lakh jobs; even as the economy shows a fragile recovery with GDP growth targeted at 6.5%, elevated NPLs near 32%, stable reserves and remittances, sweeping banking-sector reforms, and mounting external risks from Middle East conflict-driven energy and fertilizer price shocks.</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
+  </si>
+  <si>
+    <t>Bangladesh Bank Monetary Policy Statement (H1 FY27) — Summary</t>
+  </si>
+  <si>
+    <t>MPS27H1, Bangladesh Bank, Policy, FY 2026-27</t>
+  </si>
+  <si>
+    <t>Policy rate held at 10.0% (unchanged since Oct 2024); SLF at 11.5%, SDF at 7.5% — contractionary stance continues into H1FY27</t>
+  </si>
+  <si>
+    <t>Inflation: eased from 11.7% (Jul 2024) to 9.4% (May 2026); projected to moderate to ~8.9% by Dec 2026</t>
+  </si>
+  <si>
+    <t>Growth: FY26 GDP growth ~4.14%; FY27 target 6.5% (BB forecasts 6.1%)</t>
+  </si>
+  <si>
+    <t>Tk. 60,000 crore stimulus package for industry, agriculture &amp; CMSMEs — expected to create ~25 lakh jobs</t>
+  </si>
+  <si>
+    <t>Private sector credit growth slowed to 5.5% (Jun 2026); projected to recover to 8.0% by Jun 2027</t>
+  </si>
+  <si>
+    <t>NPLs remain elevated: gross NPL ratio at 32.26% (Mar 2026); new Bank Resolution Act &amp; Deposit Protection Act 2026 introduced</t>
+  </si>
+  <si>
+    <t>External sector strengthened: reserves rose to $31.74B; remittances up 19.07%; exchange rate stable (~BDT 123/USD)</t>
+  </si>
+  <si>
+    <t>Key risks: Middle East conflict, energy/fertilizer price shocks, high NPLs, weak private investment</t>
+  </si>
+  <si>
+    <t>PreparedBy</t>
   </si>
 </sst>
 </file>
@@ -636,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -667,6 +700,19 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1206,7 +1252,7 @@
         <v>39</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1219,26 +1265,26 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="87" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="7" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="72" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1263,49 +1309,49 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="11">
+        <v>122.85</v>
+      </c>
+      <c r="E2" s="11">
         <v>122.83580000000001</v>
-      </c>
-      <c r="E2" s="11">
-        <v>122.5</v>
       </c>
       <c r="F2" s="11"/>
       <c r="G2" s="10">
@@ -1315,7 +1361,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J2" s="10">
         <v>1</v>
@@ -1323,14 +1369,14 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="11">
-        <v>123.5</v>
+        <v>123.75</v>
       </c>
       <c r="E3" s="11">
         <v>123.5</v>
@@ -1343,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J3" s="10">
         <v>1</v>
@@ -1351,19 +1397,19 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>61</v>
-      </c>
       <c r="D4" s="11">
+        <v>3.7520199999999999</v>
+      </c>
+      <c r="E4" s="11">
         <v>3.7322199999999999</v>
-      </c>
-      <c r="E4" s="11">
-        <v>3.7442700000000002</v>
       </c>
       <c r="F4" s="11"/>
       <c r="G4" s="10"/>
@@ -1371,7 +1417,7 @@
         <v>2</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J4" s="10">
         <v>1</v>
@@ -1379,19 +1425,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D5" s="11">
+        <v>3.8719199999999998</v>
+      </c>
+      <c r="E5" s="11">
         <v>3.8462700000000001</v>
-      </c>
-      <c r="E5" s="11">
-        <v>3.8647800000000001</v>
       </c>
       <c r="F5" s="11"/>
       <c r="G5" s="10"/>
@@ -1399,7 +1445,7 @@
         <v>2</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J5" s="10">
         <v>0</v>
@@ -1407,19 +1453,19 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D6" s="11">
+        <v>4.0261199999999997</v>
+      </c>
+      <c r="E6" s="11">
         <v>3.9936699999999998</v>
-      </c>
-      <c r="E6" s="11">
-        <v>4.02163</v>
       </c>
       <c r="F6" s="11"/>
       <c r="G6" s="10"/>
@@ -1427,7 +1473,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J6" s="10">
         <v>0</v>
@@ -1435,19 +1481,19 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="11">
+        <v>60</v>
+      </c>
+      <c r="D7" s="16">
+        <v>2.3349999999999999E-2</v>
+      </c>
+      <c r="E7" s="11">
         <v>2.2909999999999999</v>
-      </c>
-      <c r="E7" s="11">
-        <v>2.1</v>
       </c>
       <c r="F7" s="11"/>
       <c r="G7" s="10"/>
@@ -1455,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J7" s="10">
         <v>0</v>
@@ -1463,19 +1509,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="11">
+        <v>60</v>
+      </c>
+      <c r="D8" s="16">
+        <v>2.5649999999999999E-2</v>
+      </c>
+      <c r="E8" s="11">
         <v>2.5960000000000001</v>
-      </c>
-      <c r="E8" s="11">
-        <v>2.1800000000000002</v>
       </c>
       <c r="F8" s="11"/>
       <c r="G8" s="10"/>
@@ -1483,7 +1529,7 @@
         <v>2</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="10">
         <v>0</v>
@@ -1491,19 +1537,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="11">
+        <v>60</v>
+      </c>
+      <c r="D9" s="16">
+        <v>2.733E-2</v>
+      </c>
+      <c r="E9" s="11">
         <v>2.7639999999999998</v>
-      </c>
-      <c r="E9" s="11">
-        <v>2.2999999999999998</v>
       </c>
       <c r="F9" s="11"/>
       <c r="G9" s="10"/>
@@ -1511,7 +1557,7 @@
         <v>2</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J9" s="10">
         <v>0</v>
@@ -1519,13 +1565,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>68</v>
-      </c>
       <c r="C10" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="11">
         <v>10</v>
@@ -1539,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J10" s="10">
         <v>1</v>
@@ -1547,13 +1593,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D11" s="11">
         <v>4</v>
@@ -1567,7 +1613,7 @@
         <v>2</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11" s="10">
         <v>0</v>
@@ -1575,19 +1621,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="11">
+        <v>9.61</v>
+      </c>
+      <c r="E12" s="11">
         <v>9.75</v>
-      </c>
-      <c r="E12" s="11">
-        <v>10</v>
       </c>
       <c r="F12" s="11"/>
       <c r="G12" s="10"/>
@@ -1595,7 +1641,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J12" s="10">
         <v>1</v>
@@ -1603,19 +1649,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="C13" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D13" s="11">
+        <v>9.4398999999999997</v>
+      </c>
+      <c r="E13" s="11">
         <v>9.6984999999999992</v>
-      </c>
-      <c r="E13" s="11">
-        <v>11.2</v>
       </c>
       <c r="F13" s="11">
         <v>10.4</v>
@@ -1625,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J13" s="10">
         <v>1</v>
@@ -1633,19 +1679,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D14" s="11">
+        <v>9.7097999999999995</v>
+      </c>
+      <c r="E14" s="11">
         <v>9.89</v>
-      </c>
-      <c r="E14" s="11">
-        <v>11.35</v>
       </c>
       <c r="F14" s="11">
         <v>10.6</v>
@@ -1655,7 +1701,7 @@
         <v>2</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="10">
         <v>0</v>
@@ -1663,19 +1709,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="11">
+        <v>9.74</v>
+      </c>
+      <c r="E15" s="11">
         <v>9.9254999999999995</v>
-      </c>
-      <c r="E15" s="11">
-        <v>11.5</v>
       </c>
       <c r="F15" s="11">
         <v>10.85</v>
@@ -1685,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J15" s="10">
         <v>0</v>
@@ -1693,19 +1739,19 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D16" s="11">
         <v>10.43</v>
       </c>
       <c r="E16" s="11">
-        <v>11.55</v>
+        <v>10.43</v>
       </c>
       <c r="F16" s="11">
         <v>11</v>
@@ -1715,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J16" s="10">
         <v>0</v>
@@ -1723,19 +1769,19 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D17" s="11">
         <v>10.350199999999999</v>
       </c>
       <c r="E17" s="11">
-        <v>11.25</v>
+        <v>10.350199999999999</v>
       </c>
       <c r="F17" s="11">
         <v>10.7</v>
@@ -1745,7 +1791,7 @@
         <v>2</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J17" s="10">
         <v>0</v>
@@ -1753,19 +1799,19 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D18" s="11">
         <v>10.24</v>
       </c>
       <c r="E18" s="11">
-        <v>10.199999999999999</v>
+        <v>10.24</v>
       </c>
       <c r="F18" s="11">
         <v>9.8000000000000007</v>
@@ -1775,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -1783,19 +1829,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D19" s="11">
         <v>10.34</v>
       </c>
       <c r="E19" s="11">
-        <v>10.85</v>
+        <v>10.34</v>
       </c>
       <c r="F19" s="11">
         <v>10.3</v>
@@ -1805,7 +1851,7 @@
         <v>2</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J19" s="10">
         <v>0</v>
@@ -1813,13 +1859,13 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="C20" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D20" s="11">
         <v>9.42</v>
@@ -1835,7 +1881,7 @@
         <v>2</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -1843,13 +1889,13 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D21" s="11">
         <v>8.6300000000000008</v>
@@ -1865,7 +1911,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J21" s="10">
         <v>1</v>
@@ -1873,13 +1919,13 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="D22" s="11">
         <v>5.8</v>
@@ -1893,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -1901,16 +1947,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" s="11">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="E23" s="11">
         <v>4.4000000000000004</v>
@@ -1923,7 +1969,7 @@
         <v>2</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" s="10">
         <v>1</v>
@@ -1931,16 +1977,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" s="11">
-        <v>3.43</v>
+        <v>2.8159999999999998</v>
       </c>
       <c r="E24" s="11">
         <v>3.43</v>
@@ -1953,7 +1999,7 @@
         <v>2</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J24" s="10">
         <v>1</v>
@@ -1961,13 +2007,13 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B25" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="C25" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D25" s="11">
         <v>36.08</v>
@@ -1983,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J25" s="10">
         <v>1</v>
@@ -1991,13 +2037,13 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D26" s="11">
         <v>31.53</v>
@@ -2013,7 +2059,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J26" s="10">
         <v>1</v>
@@ -2021,16 +2067,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>93</v>
-      </c>
       <c r="D27" s="11">
-        <v>4000</v>
+        <v>4175</v>
       </c>
       <c r="E27" s="11">
         <v>4000</v>
@@ -2041,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J27" s="10">
         <v>1</v>
@@ -2049,16 +2095,16 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>95</v>
-      </c>
       <c r="D28" s="11">
-        <v>73</v>
+        <v>72.12</v>
       </c>
       <c r="E28" s="11">
         <v>73</v>
@@ -2071,7 +2117,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J28" s="10">
         <v>1</v>
@@ -2085,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="14" width="13" customWidth="1"/>
@@ -2093,51 +2139,51 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="11">
         <v>121.2</v>
@@ -2181,7 +2227,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="11">
         <v>121.4</v>
@@ -2225,7 +2271,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="11">
         <v>121.6</v>
@@ -2269,7 +2315,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B5" s="11">
         <v>121.8</v>
@@ -2313,7 +2359,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B6" s="11">
         <v>122</v>
@@ -2357,7 +2403,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="11">
         <v>122.1</v>
@@ -2401,7 +2447,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8" s="11">
         <v>122.2</v>
@@ -2445,7 +2491,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="11">
         <v>122.3</v>
@@ -2489,7 +2535,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="11">
         <v>122.35</v>
@@ -2533,7 +2579,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" s="11">
         <v>122.4</v>
@@ -2577,7 +2623,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="11">
         <v>122.45</v>
@@ -2621,7 +2667,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="11">
         <v>122.48</v>
@@ -2665,7 +2711,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" s="11">
         <v>122.5</v>
@@ -2709,7 +2755,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B15" s="11">
         <v>122.75</v>
@@ -2750,6 +2796,77 @@
       <c r="N15" s="11">
         <v>85</v>
       </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="11">
+        <v>122.85</v>
+      </c>
+      <c r="C16" s="11">
+        <v>123.75</v>
+      </c>
+      <c r="D16" s="11">
+        <v>9.61</v>
+      </c>
+      <c r="E16" s="11">
+        <v>10</v>
+      </c>
+      <c r="F16" s="11">
+        <v>9.42</v>
+      </c>
+      <c r="G16" s="11">
+        <v>8.6300000000000008</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11">
+        <v>4.2</v>
+      </c>
+      <c r="J16" s="11">
+        <v>2.8159999999999998</v>
+      </c>
+      <c r="K16" s="11">
+        <v>34.549999999999997</v>
+      </c>
+      <c r="L16" s="11">
+        <v>30</v>
+      </c>
+      <c r="M16" s="11">
+        <v>4175</v>
+      </c>
+      <c r="N16" s="11">
+        <v>72.12</v>
+      </c>
+    </row>
+    <row r="18" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="18"/>
+      <c r="W18" s="18"/>
+      <c r="X18" s="18"/>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -2768,63 +2885,63 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="7"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B3" s="7"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="7"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B7" s="7"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="10" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" s="7"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -2843,58 +2960,58 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>137</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>139</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>141</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>143</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2904,7 +3021,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2916,54 +3033,112 @@
         <v>36</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="7" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="7"/>
+        <v>145</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B5" s="7"/>
+        <v>146</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="7"/>
+        <v>146</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="B7" s="7"/>
+        <v>146</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="7"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="7"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="B8" s="7"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/bd_macro_data.xlsx
+++ b/bd_macro_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\DCM_Macro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C64FF-E722-4B8B-93C5-1D52D4890284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E1C2480-390E-4433-B543-7F9EA8E0E164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -669,7 +669,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -698,9 +698,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1489,8 +1486,8 @@
       <c r="C7" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="16">
-        <v>2.3349999999999999E-2</v>
+      <c r="D7" s="11">
+        <v>2.335</v>
       </c>
       <c r="E7" s="11">
         <v>2.2909999999999999</v>
@@ -1517,8 +1514,8 @@
       <c r="C8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="16">
-        <v>2.5649999999999999E-2</v>
+      <c r="D8" s="11">
+        <v>2.5649999999999999</v>
       </c>
       <c r="E8" s="11">
         <v>2.5960000000000001</v>
@@ -1545,8 +1542,8 @@
       <c r="C9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="16">
-        <v>2.733E-2</v>
+      <c r="D9" s="11">
+        <v>2.7330000000000001</v>
       </c>
       <c r="E9" s="11">
         <v>2.7639999999999998</v>
@@ -2798,7 +2795,7 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="16" t="s">
         <v>154</v>
       </c>
       <c r="B16" s="11">
@@ -2839,34 +2836,34 @@
         <v>72.12</v>
       </c>
     </row>
-    <row r="18" spans="2:28" s="20" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="18"/>
-      <c r="S18" s="18"/>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="18"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="18"/>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="18"/>
+    <row r="18" spans="2:28" s="19" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="17"/>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="17"/>
+      <c r="T18" s="17"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="17"/>
+      <c r="W18" s="17"/>
+      <c r="X18" s="17"/>
+      <c r="Y18" s="17"/>
+      <c r="Z18" s="17"/>
+      <c r="AA18" s="17"/>
+      <c r="AB18" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
